--- a/ИСРПО.xlsx
+++ b/ИСРПО.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vaces\Desktop\programm\course_forth\ISRPO\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Temp\ispp31\ИСРПО 02.02\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DD35EB-62EC-4C3F-970B-8BB8B978D889}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="2550" windowWidth="18750" windowHeight="13650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2475" yWindow="2550" windowWidth="18750" windowHeight="13650"/>
   </bookViews>
   <sheets>
     <sheet name="Лабораторные" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="12">
   <si>
     <t>№</t>
   </si>
@@ -80,7 +79,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -122,7 +121,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -158,11 +157,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -190,6 +202,12 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -498,7 +516,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -751,30 +769,27 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>6</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" s="12"/>
       <c r="G8" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H8" s="5">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I8" s="5">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -783,30 +798,27 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>6</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="12"/>
       <c r="G9" s="7">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H9" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I9" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -939,10 +951,12 @@
       <c r="J13" s="9"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
   </mergeCells>
-  <conditionalFormatting sqref="B2:F13">
+  <conditionalFormatting sqref="B2:F7 B10:F13 B8:E9">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"!"</formula>
     </cfRule>

--- a/ИСРПО.xlsx
+++ b/ИСРПО.xlsx
@@ -89,7 +89,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -117,6 +117,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -174,7 +186,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -192,15 +204,18 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -208,6 +223,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -531,26 +549,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-      <c r="E1" s="10"/>
-      <c r="F1" s="10"/>
-      <c r="G1" s="8" t="s">
+      <c r="C1" s="11"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="7" t="s">
         <v>4</v>
       </c>
     </row>
@@ -573,8 +591,8 @@
       <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="7">
-        <f t="shared" ref="G2:G13" si="0">COUNTIF(B2:F2,"!")</f>
+      <c r="G2" s="14">
+        <f t="shared" ref="G2:G6" si="0">COUNTIF(B2:F2,"!")</f>
         <v>0</v>
       </c>
       <c r="H2" s="5">
@@ -584,7 +602,7 @@
       <c r="I2" s="5">
         <v>5</v>
       </c>
-      <c r="J2" s="9"/>
+      <c r="J2" s="8"/>
       <c r="L2" s="2" t="s">
         <v>5</v>
       </c>
@@ -611,7 +629,7 @@
       <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -622,7 +640,7 @@
       <c r="I3" s="5">
         <v>5</v>
       </c>
-      <c r="J3" s="9"/>
+      <c r="J3" s="8"/>
       <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
@@ -649,7 +667,7 @@
       <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -660,7 +678,7 @@
       <c r="I4" s="5">
         <v>5</v>
       </c>
-      <c r="J4" s="9"/>
+      <c r="J4" s="8"/>
       <c r="L4" s="4" t="s">
         <v>7</v>
       </c>
@@ -687,7 +705,7 @@
       <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -698,7 +716,7 @@
       <c r="I5" s="5">
         <v>5</v>
       </c>
-      <c r="J5" s="9"/>
+      <c r="J5" s="8"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
@@ -717,11 +735,11 @@
         <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="7">
-        <f t="shared" si="0"/>
-        <v>4</v>
+        <v>7</v>
+      </c>
+      <c r="G6" s="14">
+        <f>COUNTIF(B6:F6,"!") + COUNTIF(B6:F6,"+")</f>
+        <v>5</v>
       </c>
       <c r="H6" s="5">
         <f t="shared" si="1"/>
@@ -730,7 +748,7 @@
       <c r="I6" s="5">
         <v>5</v>
       </c>
-      <c r="J6" s="9"/>
+      <c r="J6" s="8"/>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
@@ -749,20 +767,20 @@
         <v>5</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G7" s="7">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="H7" s="5">
+        <v>5</v>
+      </c>
+      <c r="G7" s="9">
+        <f>COUNTIF(B7:F7,"!") + COUNTIF(B7:F7,"+")</f>
+        <v>5</v>
+      </c>
+      <c r="H7" s="10">
         <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I7" s="5">
-        <v>5</v>
-      </c>
-      <c r="J7" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="I7" s="10">
+        <v>5</v>
+      </c>
+      <c r="J7" s="8"/>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
@@ -777,50 +795,50 @@
       <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="7">
-        <v>3</v>
-      </c>
-      <c r="H8" s="5">
+      <c r="E8" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="13"/>
+      <c r="G8" s="9">
+        <f t="shared" ref="G8:G13" si="2">COUNTIF(B8:F8,"!") + COUNTIF(B8:F8,"+")</f>
+        <v>4</v>
+      </c>
+      <c r="H8" s="10">
         <f t="shared" si="1"/>
-        <v>3</v>
-      </c>
-      <c r="I8" s="5">
         <v>4</v>
       </c>
-      <c r="J8" s="9"/>
+      <c r="I8" s="10">
+        <v>4</v>
+      </c>
+      <c r="J8" s="8"/>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="7">
+        <v>5</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="13"/>
+      <c r="G9" s="9">
         <v>8</v>
       </c>
-      <c r="H9" s="5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="H9" s="10">
         <v>8</v>
       </c>
-      <c r="J9" s="9"/>
+      <c r="I9" s="10">
+        <v>8</v>
+      </c>
+      <c r="J9" s="8"/>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
@@ -841,8 +859,8 @@
       <c r="F10" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="7">
-        <f t="shared" si="0"/>
+      <c r="G10" s="14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H10" s="5">
@@ -852,7 +870,7 @@
       <c r="I10" s="5">
         <v>5</v>
       </c>
-      <c r="J10" s="9"/>
+      <c r="J10" s="8"/>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
@@ -873,8 +891,8 @@
       <c r="F11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="7">
-        <f t="shared" si="0"/>
+      <c r="G11" s="14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H11" s="5">
@@ -884,7 +902,7 @@
       <c r="I11" s="5">
         <v>5</v>
       </c>
-      <c r="J11" s="9"/>
+      <c r="J11" s="8"/>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
@@ -905,8 +923,8 @@
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="7">
-        <f t="shared" si="0"/>
+      <c r="G12" s="14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H12" s="5">
@@ -916,7 +934,7 @@
       <c r="I12" s="5">
         <v>5</v>
       </c>
-      <c r="J12" s="9"/>
+      <c r="J12" s="8"/>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
@@ -937,8 +955,8 @@
       <c r="F13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="7">
-        <f t="shared" si="0"/>
+      <c r="G13" s="14">
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="H13" s="5">
@@ -948,7 +966,7 @@
       <c r="I13" s="5">
         <v>5</v>
       </c>
-      <c r="J13" s="9"/>
+      <c r="J13" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/ИСРПО.xlsx
+++ b/ИСРПО.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="12">
   <si>
     <t>№</t>
   </si>
@@ -216,6 +216,9 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -223,9 +226,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -552,13 +552,13 @@
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
       <c r="G1" s="7" t="s">
         <v>11</v>
       </c>
@@ -591,8 +591,8 @@
       <c r="F2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="14">
-        <f t="shared" ref="G2:G6" si="0">COUNTIF(B2:F2,"!")</f>
+      <c r="G2" s="11">
+        <f t="shared" ref="G2:G5" si="0">COUNTIF(B2:F2,"!")</f>
         <v>0</v>
       </c>
       <c r="H2" s="5">
@@ -629,7 +629,7 @@
       <c r="F3" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="14">
+      <c r="G3" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -667,7 +667,7 @@
       <c r="F4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="14">
+      <c r="G4" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -705,7 +705,7 @@
       <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="14">
+      <c r="G5" s="11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -723,29 +723,29 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="G6" s="14">
+        <v>5</v>
+      </c>
+      <c r="G6" s="9">
         <f>COUNTIF(B6:F6,"!") + COUNTIF(B6:F6,"+")</f>
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6" s="10">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="I6" s="10">
         <v>5</v>
       </c>
       <c r="J6" s="8"/>
@@ -795,10 +795,10 @@
       <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F8" s="13"/>
+      <c r="E8" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="14"/>
       <c r="G8" s="9">
         <f t="shared" ref="G8:G13" si="2">COUNTIF(B8:F8,"!") + COUNTIF(B8:F8,"+")</f>
         <v>4</v>
@@ -825,10 +825,10 @@
       <c r="D9" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="13"/>
+      <c r="E9" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="F9" s="14"/>
       <c r="G9" s="9">
         <v>8</v>
       </c>
@@ -845,30 +845,29 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="C10" s="5">
+        <v>3</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="G10" s="14">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="F10" s="5">
+        <v>8</v>
+      </c>
+      <c r="G10" s="11">
+        <v>6</v>
       </c>
       <c r="H10" s="5">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="I10" s="5">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J10" s="8"/>
     </row>
@@ -891,7 +890,7 @@
       <c r="F11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -923,7 +922,7 @@
       <c r="F12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G12" s="14">
+      <c r="G12" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -955,7 +954,7 @@
       <c r="F13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="11">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
@@ -974,7 +973,7 @@
     <mergeCell ref="E8:F8"/>
     <mergeCell ref="E9:F9"/>
   </mergeCells>
-  <conditionalFormatting sqref="B2:F7 B10:F13 B8:E9">
+  <conditionalFormatting sqref="B10:F13 B8:E9 B2:F7">
     <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>"!"</formula>
     </cfRule>
